--- a/experimentos.xlsx
+++ b/experimentos.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Experimento A" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Experimento B" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Experimento C" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -154,7 +155,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="18">
     <dxf>
       <font>
         <b val="0"/>
@@ -321,6 +322,12 @@
       </font>
       <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -359,6 +366,21 @@
     <tableColumn id="4" name="Undersampling" dataDxfId="9"/>
     <tableColumn id="5" name="SMOTE" dataDxfId="10"/>
     <tableColumn id="6" name="Prepración" dataDxfId="11"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" displayName="Tabla2" ref="A1:F18">
+  <autoFilter ref="A1:F18"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Columna1" dataDxfId="12"/>
+    <tableColumn id="2" name="Nº filas" dataDxfId="13"/>
+    <tableColumn id="3" name="Preprocesamiento" dataDxfId="14"/>
+    <tableColumn id="4" name="Undersampling" dataDxfId="15"/>
+    <tableColumn id="5" name="SMOTE" dataDxfId="16"/>
+    <tableColumn id="6" name="Prepración" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1623,4 +1645,339 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" customWidth="1" min="1" max="1" width="38.7109375"/>
+    <col customWidth="1" min="2" max="2" width="17.42578125"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="27"/>
+    <col bestFit="1" customWidth="1" min="4" max="4" width="22.42578125"/>
+    <col customWidth="1" min="5" max="5" width="17.42578125"/>
+    <col customWidth="1" min="6" max="6" width="19.5703125"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21.75">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="21.75">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2">
+        <v>13484708</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2">
+        <v>2670478</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2670478</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" ht="21.75">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2">
+        <v>576191</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2">
+        <v>576175</v>
+      </c>
+      <c r="E3" s="2">
+        <v>576175</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" ht="21.75">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2">
+        <v>686012</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2">
+        <v>668461</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" ht="21.75">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2">
+        <v>461912</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2">
+        <v>434873</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" ht="21.75">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2">
+        <v>286191</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2">
+        <v>282310</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" ht="21.75">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <v>161934</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2">
+        <v>160604</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" ht="21.75">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2">
+        <v>187589</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2">
+        <v>117322</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" ht="21.75">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2">
+        <v>41508</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2">
+        <v>41455</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" ht="21.75">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="2">
+        <v>10990</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2">
+        <v>10285</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" ht="21.75">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1730</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2">
+        <v>1730</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" ht="21.75">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2">
+        <v>611</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2">
+        <v>611</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" ht="21.75">
+      <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="2">
+        <v>230</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2">
+        <v>230</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" ht="21.75">
+      <c r="A14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="2">
+        <v>87</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2">
+        <v>87</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" ht="21.75">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="2">
+        <v>139890</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2">
+        <v>19462</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" ht="21.75">
+      <c r="A16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="2">
+        <v>193360</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2">
+        <v>39346</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" ht="21.75">
+      <c r="A17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="2">
+        <f>SUM(B2)</f>
+        <v>13484708</v>
+      </c>
+      <c r="C17" s="2">
+        <f>SUM(C2)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <f>SUM(D2)</f>
+        <v>2670478</v>
+      </c>
+      <c r="E17" s="2">
+        <f>SUM(E2)</f>
+        <v>2670478</v>
+      </c>
+      <c r="F17" s="2">
+        <f>SUM(F2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="21.75">
+      <c r="A18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="2">
+        <f>SUM(B3:B16)</f>
+        <v>2748235</v>
+      </c>
+      <c r="C18" s="2">
+        <f>SUM(C3:C16)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <f>SUM(D3:D16)</f>
+        <v>2352951</v>
+      </c>
+      <c r="E18" s="2">
+        <f>SUM(E3:E16)</f>
+        <v>576175</v>
+      </c>
+      <c r="F18" s="2">
+        <f>SUM(F3:F16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="21.75">
+      <c r="A19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="2">
+        <f>SUM(B2:B16)</f>
+        <v>16232943</v>
+      </c>
+      <c r="C19" s="2">
+        <f>SUM(C2:C16)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <f>SUM(D2:D16)</f>
+        <v>5023429</v>
+      </c>
+      <c r="E19" s="2">
+        <f>SUM(E2:E16)</f>
+        <v>3246653</v>
+      </c>
+      <c r="F19" s="2">
+        <f>SUM(F2:F16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="4"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="0" verticalDpi="0" copies="1"/>
+  <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>